--- a/etl/tests/fixtures/dental_registry_sample.xlsx
+++ b/etl/tests/fixtures/dental_registry_sample.xlsx
@@ -461,7 +461,8 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Szervezeti egység kódja</t>
+          <t>Szervezeti egység kódja 
+(FIN kód)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
